--- a/AAII_Financials/Yearly/OCC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OCC_YR_FIN.xlsx
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>50400</v>
+        <v>50500</v>
       </c>
       <c r="E9" s="3">
         <v>48500</v>
